--- a/Result/profitability/3710.xlsx
+++ b/Result/profitability/3710.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM34"/>
+  <dimension ref="A1:AM35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4748,6 +4748,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>3710</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2038</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1669</v>
+      </c>
+      <c r="E35" t="n">
+        <v>369</v>
+      </c>
+      <c r="F35" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-103</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-5.07%</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>-64</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-167</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-190</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="M35" t="n">
+        <v>-0.36625</v>
+      </c>
+      <c r="N35" t="n">
+        <v>19.91625</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.07999999999999996</v>
+      </c>
+      <c r="X35" t="n">
+        <v>-0.108108108108108</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0.3500000000000014</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0.01969611705120999</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>-2.885714285714286</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>-0.5999999999999979</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>-0.03205128205128194</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK35" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
